--- a/data/nursery_school/data.xlsx
+++ b/data/nursery_school/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R119"/>
+  <dimension ref="A1:R120"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7063,9 +7063,47 @@
         <v>有</v>
       </c>
     </row>
+    <row r="120">
+      <c r="B120" t="str">
+        <v/>
+      </c>
+      <c r="C120" t="str">
+        <v/>
+      </c>
+      <c r="D120" t="str">
+        <v>屋島協会幼稚園</v>
+      </c>
+      <c r="E120" t="str">
+        <v>高松市屋島屋島西町１３９２−７</v>
+      </c>
+      <c r="F120" t="str">
+        <v>087-841-1925</v>
+      </c>
+      <c r="G120" t="str">
+        <v>http://www.akaiyane.jp/</v>
+      </c>
+      <c r="I120" t="str">
+        <v>認定こども園(幼稚園型)</v>
+      </c>
+      <c r="L120" t="str">
+        <v>94</v>
+      </c>
+      <c r="M120" t="str">
+        <v>1号認定 満3歳～、2・3号認定 6か月～</v>
+      </c>
+      <c r="N120" t="str">
+        <v>月火水木金土</v>
+      </c>
+      <c r="O120" t="str">
+        <v>07:30</v>
+      </c>
+      <c r="P120" t="str">
+        <v>18:30</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R120"/>
   </ignoredErrors>
 </worksheet>
 </file>